--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Focused Equity Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Focused Equity Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="137">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Focused Equity Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -76,6 +76,30 @@
     <t>INE040A01034</t>
   </si>
   <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
     <t>Ultratech Cement Ltd.</t>
   </si>
   <si>
@@ -85,28 +109,13 @@
     <t>Cement &amp; Cement Products</t>
   </si>
   <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
   </si>
   <si>
     <t>Infosys Ltd.</t>
@@ -118,19 +127,55 @@
     <t>It - Software</t>
   </si>
   <si>
+    <t>Pidilite Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
     <t>Lupin Ltd.</t>
   </si>
   <si>
     <t>INE326A01037</t>
   </si>
   <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
+    <t>Mahindra &amp; Mahindra Ltd.</t>
+  </si>
+  <si>
+    <t>INE101A01026</t>
+  </si>
+  <si>
+    <t>Automobiles</t>
+  </si>
+  <si>
+    <t>HDFC Asset Management Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE127D01025</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
+  </si>
+  <si>
+    <t>Insurance</t>
   </si>
   <si>
     <t>NTPC Ltd.</t>
@@ -142,157 +187,121 @@
     <t>Power</t>
   </si>
   <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
     <t>TVS Motor Company Ltd.</t>
   </si>
   <si>
     <t>INE494B01023</t>
   </si>
   <si>
-    <t>Automobiles</t>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Vedanta Ltd.</t>
+  </si>
+  <si>
+    <t>INE205A01025</t>
+  </si>
+  <si>
+    <t>Diversified Metals</t>
+  </si>
+  <si>
+    <t>Adani Ports and Special Economic Zone Ltd.</t>
+  </si>
+  <si>
+    <t>INE742F01042</t>
+  </si>
+  <si>
+    <t>Transport Infrastructure</t>
+  </si>
+  <si>
+    <t>Prestige Estates Projects Ltd.</t>
+  </si>
+  <si>
+    <t>INE811K01011</t>
+  </si>
+  <si>
+    <t>Realty</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
   </si>
   <si>
     <t>Info Edge (India) Ltd.</t>
   </si>
   <si>
-    <t>INE663F01024</t>
+    <t>INE663F01032</t>
   </si>
   <si>
     <t>Retailing</t>
   </si>
   <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd.</t>
-  </si>
-  <si>
-    <t>INE016A01026</t>
+    <t>Page Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE761H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>The Phoenix Mills Ltd.</t>
+  </si>
+  <si>
+    <t>INE211B01039</t>
+  </si>
+  <si>
+    <t>Star Health &amp; Allied Insurance</t>
+  </si>
+  <si>
+    <t>INE575P01011</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd.</t>
+  </si>
+  <si>
+    <t>INE081A01020</t>
+  </si>
+  <si>
+    <t>Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Godrej Consumer Products Ltd.</t>
+  </si>
+  <si>
+    <t>INE102D01028</t>
   </si>
   <si>
     <t>Personal Products</t>
   </si>
   <si>
-    <t>Zydus Lifesciences Ltd.</t>
-  </si>
-  <si>
-    <t>INE010B01027</t>
-  </si>
-  <si>
-    <t>Pidilite Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE318A01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>Vedanta Ltd.</t>
-  </si>
-  <si>
-    <t>INE205A01025</t>
-  </si>
-  <si>
-    <t>Diversified Metals</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE761H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
-    <t>The Phoenix Mills Ltd.</t>
-  </si>
-  <si>
-    <t>INE211B01039</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>Prestige Estates Projects Ltd.</t>
-  </si>
-  <si>
-    <t>INE811K01011</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Star Health &amp; Allied Insurance</t>
-  </si>
-  <si>
-    <t>INE575P01011</t>
-  </si>
-  <si>
-    <t>Mahindra &amp; Mahindra Ltd.</t>
-  </si>
-  <si>
-    <t>INE101A01026</t>
-  </si>
-  <si>
-    <t>Shree Cements Ltd.</t>
-  </si>
-  <si>
-    <t>INE070A01015</t>
-  </si>
-  <si>
-    <t>^</t>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Hyundai Motor India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0V6F01027</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -331,34 +340,19 @@
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X383</t>
+    <t>IN002025X018</t>
   </si>
   <si>
     <t>SOV</t>
   </si>
   <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024X417</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>364 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002023Z489</t>
-  </si>
-  <si>
-    <t>IN002024Z040</t>
+    <t>IN002025X026</t>
+  </si>
+  <si>
+    <t>IN002024X490</t>
+  </si>
+  <si>
+    <t>IN002024X516</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -388,39 +382,21 @@
     <t>Stock / Index Futures</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd. $$</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd. $$</t>
-  </si>
-  <si>
-    <t>Page Industries Ltd. $$</t>
+    <t>Eternal Ltd. $$</t>
+  </si>
+  <si>
+    <t>INFO edge india Ltd $$</t>
+  </si>
+  <si>
+    <t>Tata Steel Ltd. $$</t>
+  </si>
+  <si>
+    <t>Prestige Estates Projects Ltd. $$</t>
   </si>
   <si>
     <t>Cummins India Ltd. $$</t>
   </si>
   <si>
-    <t>Pidilite Industries Ltd. $$</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd. $$</t>
-  </si>
-  <si>
-    <t>Lupin Ltd. $$</t>
-  </si>
-  <si>
-    <t>Dabur India Ltd. $$</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd. $$</t>
-  </si>
-  <si>
-    <t>Siemens Ltd. $$</t>
-  </si>
-  <si>
-    <t>TVS Motor Company Ltd. $$</t>
-  </si>
-  <si>
     <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
   </si>
   <si>
@@ -430,16 +406,13 @@
     <t>$$ - Derivatives.</t>
   </si>
   <si>
-    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
-  </si>
-  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -451,18 +424,17 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - BSE 500 TRI</t>
+    <t>Benchmark name - S&amp;P BSE 500 TRI 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="\^"/>
-    <numFmt numFmtId="180" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -652,7 +624,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -704,7 +676,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -713,10 +685,6 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -827,13 +795,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -851,7 +819,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="21602700"/>
+          <a:off x="666750" y="19888200"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -866,13 +834,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -890,7 +858,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="24460200"/>
+          <a:off x="666750" y="22745700"/>
           <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1224,19 +1192,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J125"/>
+  <dimension ref="B1:J116"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.857142857142854" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.857142857142858" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.0" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.857142857142854" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.0" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1324,10 +1292,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>965071.7500000001</v>
+        <v>1130897.9699999997</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9588846956774</v>
+        <v>0.9693391847818001</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1361,10 +1329,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>965071.7500000001</v>
+        <v>1130897.9699999997</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9588846956774</v>
+        <v>0.9693391847818001</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1387,13 +1355,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>6986303</v>
+        <v>6571303</v>
       </c>
       <c r="G8" s="15">
-        <v>87524.40</v>
+        <v>95007.90</v>
       </c>
       <c r="H8" s="16">
-        <v>0.086963282946</v>
+        <v>0.0814351805176</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1416,13 +1384,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="14">
-        <v>4430854</v>
+        <v>3772593</v>
       </c>
       <c r="G9" s="15">
-        <v>75269.13</v>
+        <v>73373.16</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0747865812195</v>
+        <v>0.0628911546276</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1442,16 +1410,16 @@
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>506033</v>
+        <v>5696833</v>
       </c>
       <c r="G10" s="15">
-        <v>58130.29</v>
+        <v>67917.64</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0577576179557</v>
+        <v>0.0582150039494</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1462,25 +1430,25 @@
     </row>
     <row r="11" spans="2:10" ht="15" customHeight="1">
       <c r="B11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="F11" s="14">
-        <v>5839940</v>
+        <v>3116002</v>
       </c>
       <c r="G11" s="15">
-        <v>57587.65</v>
+        <v>52274.05</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0572184568091</v>
+        <v>0.044806239251</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1503,13 +1471,13 @@
         <v>27</v>
       </c>
       <c r="F12" s="14">
-        <v>3019645</v>
+        <v>2765934</v>
       </c>
       <c r="G12" s="15">
-        <v>52661.10</v>
+        <v>51341.27</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0523234908156</v>
+        <v>0.0440067151305</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1532,13 +1500,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="14">
-        <v>2439407</v>
+        <v>447101</v>
       </c>
       <c r="G13" s="15">
-        <v>39672.08</v>
+        <v>50120.02</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0394177431447</v>
+        <v>0.042959931503</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1561,13 +1529,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="14">
-        <v>2034334</v>
+        <v>1299589</v>
       </c>
       <c r="G14" s="15">
-        <v>38241.41</v>
+        <v>47761.20</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0379962451394</v>
+        <v>0.0409380898192</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1587,16 +1555,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F15" s="14">
-        <v>1710918</v>
+        <v>2980807</v>
       </c>
       <c r="G15" s="15">
-        <v>35594.79</v>
+        <v>46581.07</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0353665925636</v>
+        <v>0.0399265518357</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1607,25 +1575,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" s="14">
-        <v>993958</v>
+        <v>1357638</v>
       </c>
       <c r="G16" s="15">
-        <v>35458.46</v>
+        <v>42184.53</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0352311365723</v>
+        <v>0.0361580964909</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1636,25 +1604,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" s="14">
-        <v>10442972</v>
+        <v>2951512</v>
       </c>
       <c r="G17" s="15">
-        <v>33835.23</v>
+        <v>41938.03</v>
       </c>
       <c r="H17" s="16">
-        <v>0.033618313065</v>
+        <v>0.0359468111978</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1665,25 +1633,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F18" s="14">
-        <v>1364051</v>
+        <v>2074222</v>
       </c>
       <c r="G18" s="15">
-        <v>33527.01</v>
+        <v>40607.04</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0333120690569</v>
+        <v>0.0348059649006</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1706,13 +1674,13 @@
         <v>47</v>
       </c>
       <c r="F19" s="14">
-        <v>413470</v>
+        <v>1280069</v>
       </c>
       <c r="G19" s="15">
-        <v>31935.18</v>
+        <v>38105.09</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0317304442449</v>
+        <v>0.0326614406043</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1735,13 +1703,13 @@
         <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>1077738</v>
+        <v>755413</v>
       </c>
       <c r="G20" s="15">
-        <v>31405.82</v>
+        <v>36131.40</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0312044779605</v>
+        <v>0.030969709691</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1764,13 +1732,13 @@
         <v>53</v>
       </c>
       <c r="F21" s="14">
-        <v>5607708</v>
+        <v>2299594</v>
       </c>
       <c r="G21" s="15">
-        <v>29712.44</v>
+        <v>34556</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0295219541834</v>
+        <v>0.0296193695257</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1790,16 +1758,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="F22" s="14">
-        <v>2897592</v>
+        <v>10158746</v>
       </c>
       <c r="G22" s="15">
-        <v>28113.89</v>
+        <v>33920.05</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0279336524533</v>
+        <v>0.0290742706124</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1810,25 +1778,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" s="14">
-        <v>961524</v>
+        <v>615242</v>
       </c>
       <c r="G23" s="15">
-        <v>27612.08</v>
+        <v>33902.91</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0274350595464</v>
+        <v>0.0290595792131</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -1839,25 +1807,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F24" s="14">
-        <v>2025000</v>
+        <v>1101848</v>
       </c>
       <c r="G24" s="15">
-        <v>25618.28</v>
+        <v>30640.19</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0254540417555</v>
+        <v>0.0262629676452</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -1880,13 +1848,13 @@
         <v>64</v>
       </c>
       <c r="F25" s="14">
-        <v>5800829</v>
+        <v>933675</v>
       </c>
       <c r="G25" s="15">
-        <v>25604.86</v>
+        <v>30513.43</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0254407077908</v>
+        <v>0.0261543164332</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -1909,13 +1877,13 @@
         <v>67</v>
       </c>
       <c r="F26" s="14">
-        <v>56488</v>
+        <v>6546823</v>
       </c>
       <c r="G26" s="15">
-        <v>25263.44</v>
+        <v>28514.69</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0251014766272</v>
+        <v>0.0244411141342</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -1938,13 +1906,13 @@
         <v>70</v>
       </c>
       <c r="F27" s="14">
-        <v>1482339</v>
+        <v>1875495</v>
       </c>
       <c r="G27" s="15">
-        <v>24337.04</v>
+        <v>26872.09</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0241810157577</v>
+        <v>0.0230331740838</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -1964,16 +1932,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F28" s="14">
-        <v>1789556</v>
+        <v>1827827</v>
       </c>
       <c r="G28" s="15">
-        <v>24329.01</v>
+        <v>26806.91</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0241730372379</v>
+        <v>0.0229773056237</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -1984,25 +1952,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F29" s="14">
-        <v>2109737</v>
+        <v>1360452</v>
       </c>
       <c r="G29" s="15">
-        <v>23539.39</v>
+        <v>24654.11</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0233884794748</v>
+        <v>0.0211320521593</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2022,16 +1990,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F30" s="14">
-        <v>1577557</v>
+        <v>1713090</v>
       </c>
       <c r="G30" s="15">
-        <v>23404.64</v>
+        <v>24454.36</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0232545933541</v>
+        <v>0.0209608382149</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2042,25 +2010,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F31" s="14">
-        <v>500847</v>
+        <v>52393</v>
       </c>
       <c r="G31" s="15">
-        <v>21658.38</v>
+        <v>24299.87</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0215195285896</v>
+        <v>0.0208284184789</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2071,25 +2039,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F32" s="14">
-        <v>588677</v>
+        <v>1551798</v>
       </c>
       <c r="G32" s="15">
-        <v>21572.95</v>
+        <v>23852.69</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0214346462795</v>
+        <v>0.0204451221001</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2100,25 +2068,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="F33" s="14">
-        <v>346778</v>
+        <v>4829784</v>
       </c>
       <c r="G33" s="15">
-        <v>21061.04</v>
+        <v>23069.46</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0209260181236</v>
+        <v>0.0197737834384</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2138,16 +2106,16 @@
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="F34" s="14">
-        <v>3767029</v>
+        <v>13847000</v>
       </c>
       <c r="G34" s="15">
-        <v>16320.65</v>
+        <v>22296.44</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0162160186623</v>
+        <v>0.0191111961879</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2158,25 +2126,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F35" s="14">
-        <v>537801</v>
+        <v>1793000</v>
       </c>
       <c r="G35" s="15">
-        <v>16079.44</v>
+        <v>22079</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0159763550545</v>
+        <v>0.0189248194165</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2187,25 +2155,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F36" s="14">
-        <v>6</v>
+        <v>8826001</v>
       </c>
       <c r="G36" s="15">
-        <v>1.67</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>92</v>
+        <v>21033.24</v>
+      </c>
+      <c r="H36" s="16">
+        <v>0.0180284554891</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2216,6 +2184,27 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="14">
+        <v>871055</v>
+      </c>
+      <c r="G37" s="15">
+        <v>16090.13</v>
+      </c>
+      <c r="H37" s="16">
+        <v>0.0137915125068</v>
+      </c>
+      <c r="I37" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J37" s="11" t="s">
@@ -2223,28 +2212,7 @@
       </c>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
-      <c r="B38" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I38" s="9" t="s">
+      <c r="B38" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J38" s="11" t="s">
@@ -2252,7 +2220,28 @@
       </c>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J39" s="11" t="s">
@@ -2260,28 +2249,7 @@
       </c>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
-      <c r="B40" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I40" s="9" t="s">
+      <c r="B40" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J40" s="11" t="s">
@@ -2289,7 +2257,28 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
@@ -2297,36 +2286,36 @@
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" ht="15" customHeight="1">
+      <c r="B43" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1">
-      <c r="B43" s="12" t="s">
+      <c r="C43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J43" s="11" t="s">
@@ -2334,28 +2323,7 @@
       </c>
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J44" s="11" t="s">
@@ -2363,7 +2331,28 @@
       </c>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I45" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J45" s="11" t="s">
@@ -2371,36 +2360,36 @@
       </c>
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="15" customHeight="1">
+      <c r="B47" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" ht="15" customHeight="1">
-      <c r="B47" s="12" t="s">
+      <c r="H47" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I47" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J47" s="11" t="s">
@@ -2408,28 +2397,7 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J48" s="11" t="s">
@@ -2437,7 +2405,28 @@
       </c>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I49" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -2445,28 +2434,7 @@
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I50" s="9" t="s">
+      <c r="B50" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -2474,7 +2442,28 @@
       </c>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I51" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J51" s="11" t="s">
@@ -2482,28 +2471,7 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
-      <c r="B52" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="9">
-        <v>16425</v>
-      </c>
-      <c r="H52" s="10">
-        <v>0.0163196996765</v>
-      </c>
-      <c r="I52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J52" s="11" t="s">
@@ -2511,7 +2479,28 @@
       </c>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="9">
+        <v>14927.55</v>
+      </c>
+      <c r="H53" s="10">
+        <v>0.0127950173504</v>
+      </c>
+      <c r="I53" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J53" s="11" t="s">
@@ -2519,28 +2508,7 @@
       </c>
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
-      <c r="B54" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H54" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I54" s="9" t="s">
+      <c r="B54" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J54" s="11" t="s">
@@ -2548,7 +2516,28 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I55" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J55" s="11" t="s">
@@ -2556,28 +2545,7 @@
       </c>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
-      <c r="B56" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H56" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I56" s="9" t="s">
+      <c r="B56" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J56" s="11" t="s">
@@ -2585,7 +2553,28 @@
       </c>
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I57" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J57" s="11" t="s">
@@ -2593,28 +2582,7 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
-      <c r="B58" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G58" s="9">
-        <v>16425</v>
-      </c>
-      <c r="H58" s="10">
-        <v>0.0163196996765</v>
-      </c>
-      <c r="I58" s="9" t="s">
+      <c r="B58" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J58" s="11" t="s">
@@ -2622,29 +2590,29 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
-      <c r="B59" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="13" t="s">
+      <c r="B59" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F59" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="G59" s="15">
-        <v>4952.06</v>
-      </c>
-      <c r="H59" s="16">
-        <v>0.0049203124493</v>
-      </c>
-      <c r="I59" s="15">
-        <v>6.43</v>
+      <c r="C59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="9">
+        <v>14927.55</v>
+      </c>
+      <c r="H59" s="10">
+        <v>0.0127950173504</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2652,28 +2620,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F60" s="14">
-        <v>3800000</v>
+        <v>7500000</v>
       </c>
       <c r="G60" s="15">
-        <v>3745.20</v>
+        <v>7463.21</v>
       </c>
       <c r="H60" s="16">
-        <v>0.003721189603</v>
+        <v>0.0063970243905</v>
       </c>
       <c r="I60" s="15">
-        <v>6.51</v>
+        <v>5.62</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -2681,28 +2649,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F61" s="14">
-        <v>2800000</v>
+        <v>5000000</v>
       </c>
       <c r="G61" s="15">
-        <v>2763</v>
+        <v>4969.50</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0027452864661</v>
+        <v>0.0042595629372</v>
       </c>
       <c r="I61" s="15">
-        <v>6.52</v>
+        <v>5.60</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -2710,28 +2678,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C62" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>106</v>
-      </c>
       <c r="F62" s="14">
-        <v>2500000</v>
+        <v>2100000</v>
       </c>
       <c r="G62" s="15">
-        <v>2469.99</v>
+        <v>2096.40</v>
       </c>
       <c r="H62" s="16">
-        <v>0.002454154947</v>
+        <v>0.0017969107036</v>
       </c>
       <c r="I62" s="15">
-        <v>6.52</v>
+        <v>5.70</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -2739,28 +2707,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F63" s="14">
-        <v>2000000</v>
+        <v>400000</v>
       </c>
       <c r="G63" s="15">
-        <v>1998.26</v>
+        <v>398.44</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0019854491979</v>
+        <v>0.0003415193191</v>
       </c>
       <c r="I63" s="15">
-        <v>6.37</v>
+        <v>5.70</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -2768,57 +2736,36 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C64" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D64" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F64" s="14">
-        <v>300000</v>
-      </c>
-      <c r="G64" s="15">
-        <v>299.37</v>
-      </c>
-      <c r="H64" s="16">
-        <v>0.0002974507453</v>
-      </c>
-      <c r="I64" s="15">
-        <v>6.42</v>
-      </c>
-      <c r="J64" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" ht="15" customHeight="1">
-      <c r="B65" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="F65" s="14">
-        <v>200000</v>
-      </c>
-      <c r="G65" s="15">
-        <v>197.12</v>
-      </c>
-      <c r="H65" s="16">
-        <v>0.0001958562679</v>
-      </c>
-      <c r="I65" s="15">
-        <v>6.51</v>
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -2834,7 +2781,7 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>13</v>
@@ -2849,10 +2796,10 @@
         <v>13</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I67" s="9" t="s">
         <v>13</v>
@@ -2871,7 +2818,7 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>13</v>
@@ -2885,11 +2832,11 @@
       <c r="F69" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G69" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>94</v>
+      <c r="G69" s="9">
+        <v>22606.81</v>
+      </c>
+      <c r="H69" s="10">
+        <v>0.0193772270861</v>
       </c>
       <c r="I69" s="9" t="s">
         <v>13</v>
@@ -2908,7 +2855,7 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>13</v>
@@ -2923,10 +2870,10 @@
         <v>13</v>
       </c>
       <c r="G71" s="9">
-        <v>15524.23</v>
+        <v>2700.0000004000003</v>
       </c>
       <c r="H71" s="10">
-        <v>0.0154247044939</v>
+        <v>0.0023142811011</v>
       </c>
       <c r="I71" s="9" t="s">
         <v>13</v>
@@ -2937,6 +2884,20 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="13"/>
+      <c r="D72" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="13"/>
+      <c r="G72" s="15">
+        <v>2700.0000004000003</v>
+      </c>
+      <c r="H72" s="16">
+        <v>0.0023142811011</v>
+      </c>
+      <c r="I72" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
@@ -2944,188 +2905,191 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9">
-        <v>6500.000000399999</v>
-      </c>
-      <c r="H73" s="10">
-        <v>0.0064583286396</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
+      <c r="C74" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="18">
+        <v>-4463.337605979992</v>
+      </c>
+      <c r="H74" s="19">
+        <v>-0.003825710321502275</v>
+      </c>
+      <c r="I74" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="13"/>
-      <c r="G74" s="15">
-        <v>6500.000000399999</v>
-      </c>
-      <c r="H74" s="16">
-        <v>0.0064583286396</v>
-      </c>
-      <c r="I74" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="18" t="s">
+      <c r="C75" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="18">
+        <v>1166668.99239442</v>
+      </c>
+      <c r="H75" s="19">
+        <v>0.9999999999978977</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="15" customHeight="1">
+      <c r="B77" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C76" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G76" s="19">
-        <v>2931.3644253499806</v>
-      </c>
-      <c r="H76" s="20">
-        <v>0.002912571510797687</v>
-      </c>
-      <c r="I76" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="18" t="s">
+      <c r="C77" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" ht="15" customHeight="1">
+      <c r="B78" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E78" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" ht="15" customHeight="1">
+      <c r="B79" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C77" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="19">
-        <v>1006452.34442575</v>
-      </c>
-      <c r="H77" s="20">
-        <v>0.9999999999981977</v>
-      </c>
-      <c r="I77" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" ht="15" customHeight="1">
-      <c r="B79" s="19" t="s">
+      <c r="C79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C79" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" ht="15" customHeight="1">
-      <c r="B80" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G80" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H80" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
+      <c r="C80" s="13"/>
+      <c r="D80" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80" s="14">
+        <v>4800000</v>
+      </c>
+      <c r="G80" s="15">
+        <v>11515.68</v>
+      </c>
+      <c r="H80" s="16">
+        <v>0.0098705631803</v>
+      </c>
+      <c r="I80" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H81" s="8" t="s">
+      <c r="C81" s="13"/>
+      <c r="D81" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F81" s="14">
+        <v>187500</v>
+      </c>
+      <c r="G81" s="15">
+        <v>2688.75</v>
+      </c>
+      <c r="H81" s="16">
+        <v>0.0023046382628</v>
+      </c>
+      <c r="I81" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3138,16 +3102,16 @@
         <v>13</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="F82" s="14">
-        <v>140000</v>
+        <v>1116500</v>
       </c>
       <c r="G82" s="15">
-        <v>1760.43</v>
+        <v>1807.61</v>
       </c>
       <c r="H82" s="16">
-        <v>0.0017491439209</v>
+        <v>0.0015493769113</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>13</v>
@@ -3165,16 +3129,16 @@
         <v>13</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="F83" s="14">
-        <v>73500</v>
+        <v>37700</v>
       </c>
       <c r="G83" s="15">
-        <v>1282.39</v>
+        <v>556.34</v>
       </c>
       <c r="H83" s="16">
-        <v>0.0012741686251</v>
+        <v>0.0004768619065</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>13</v>
@@ -3192,16 +3156,16 @@
         <v>13</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F84" s="14">
-        <v>2580</v>
+        <v>-45000</v>
       </c>
       <c r="G84" s="15">
-        <v>1153.91</v>
+        <v>-1476.45</v>
       </c>
       <c r="H84" s="16">
-        <v>0.0011465123077</v>
+        <v>-0.0012655260486</v>
       </c>
       <c r="I84" s="15" t="s">
         <v>13</v>
@@ -3210,340 +3174,112 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="12" t="s">
+    <row r="88" spans="2:9" ht="15" customHeight="1">
+      <c r="B88" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F85" s="14">
-        <v>29700</v>
-      </c>
-      <c r="G85" s="15">
-        <v>865.41</v>
-      </c>
-      <c r="H85" s="16">
-        <v>0.000859861875</v>
-      </c>
-      <c r="I85" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
+      <c r="C88" s="21"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="21"/>
+      <c r="F88" s="21"/>
+      <c r="G88" s="21"/>
+      <c r="H88" s="21"/>
+      <c r="I88" s="21"/>
+    </row>
+    <row r="92" spans="2:9" ht="15" customHeight="1">
+      <c r="B92" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F86" s="14">
-        <v>25000</v>
-      </c>
-      <c r="G86" s="15">
-        <v>722.31</v>
-      </c>
-      <c r="H86" s="16">
-        <v>0.000717679286</v>
-      </c>
-      <c r="I86" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="12" t="s">
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="21"/>
+      <c r="G92" s="21"/>
+      <c r="H92" s="21"/>
+      <c r="I92" s="21"/>
+    </row>
+    <row r="93" spans="2:8" ht="15" customHeight="1">
+      <c r="B93" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F87" s="14">
-        <v>2500</v>
-      </c>
-      <c r="G87" s="15">
-        <v>289.45</v>
-      </c>
-      <c r="H87" s="16">
-        <v>0.0002875943422</v>
-      </c>
-      <c r="I87" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="21"/>
+      <c r="G93" s="21"/>
+      <c r="H93" s="21"/>
+    </row>
+    <row r="94" spans="2:8" ht="15" customHeight="1">
+      <c r="B94" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88" s="14">
-        <v>8925</v>
-      </c>
-      <c r="G88" s="15">
-        <v>186.41</v>
-      </c>
-      <c r="H88" s="16">
-        <v>0.0001852149294</v>
-      </c>
-      <c r="I88" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="12" t="s">
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="21"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="21"/>
+    </row>
+    <row r="95" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B95" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F89" s="14">
-        <v>-237500</v>
-      </c>
-      <c r="G89" s="15">
-        <v>-1265.52</v>
-      </c>
-      <c r="H89" s="16">
-        <v>-0.0012574067783</v>
-      </c>
-      <c r="I89" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="21"/>
+      <c r="G95" s="21"/>
+      <c r="H95" s="21"/>
+    </row>
+    <row r="96" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B96" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F90" s="14">
-        <v>-36000</v>
-      </c>
-      <c r="G90" s="15">
-        <v>-1324.89</v>
-      </c>
-      <c r="H90" s="16">
-        <v>-0.0013163961585</v>
-      </c>
-      <c r="I90" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="12" t="s">
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="21"/>
+      <c r="F96" s="21"/>
+      <c r="G96" s="21"/>
+      <c r="H96" s="21"/>
+    </row>
+    <row r="97" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B97" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C91" s="13"/>
-      <c r="D91" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F91" s="14">
-        <v>-33000</v>
-      </c>
-      <c r="G91" s="15">
-        <v>-2012.67</v>
-      </c>
-      <c r="H91" s="16">
-        <v>-0.0019997668157</v>
-      </c>
-      <c r="I91" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="21"/>
+      <c r="G97" s="21"/>
+      <c r="H97" s="21"/>
+    </row>
+    <row r="100" ht="15">
+      <c r="B100" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F92" s="14">
-        <v>-82250</v>
-      </c>
-      <c r="G92" s="15">
-        <v>-2027.71</v>
-      </c>
-      <c r="H92" s="16">
-        <v>-0.0020147103946</v>
-      </c>
-      <c r="I92" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" ht="15" customHeight="1">
-      <c r="B96" s="13" t="s">
+    </row>
+    <row r="115" ht="15">
+      <c r="B115" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22"/>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="22"/>
-      <c r="I96" s="22"/>
-    </row>
-    <row r="100" spans="2:9" ht="15" customHeight="1">
-      <c r="B100" s="13" t="s">
+    </row>
+    <row r="116" ht="15">
+      <c r="B116" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22"/>
-      <c r="E100" s="22"/>
-      <c r="F100" s="22"/>
-      <c r="G100" s="22"/>
-      <c r="H100" s="22"/>
-      <c r="I100" s="22"/>
-    </row>
-    <row r="101" spans="2:8" ht="15" customHeight="1">
-      <c r="B101" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C101" s="22"/>
-      <c r="D101" s="22"/>
-      <c r="E101" s="22"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="22"/>
-      <c r="H101" s="22"/>
-    </row>
-    <row r="102" spans="2:8" ht="15" customHeight="1">
-      <c r="B102" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="22"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="22"/>
-      <c r="H102" s="22"/>
-    </row>
-    <row r="103" spans="2:8" ht="15" customHeight="1">
-      <c r="B103" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="C103" s="22"/>
-      <c r="D103" s="22"/>
-      <c r="E103" s="22"/>
-      <c r="F103" s="22"/>
-      <c r="G103" s="22"/>
-      <c r="H103" s="22"/>
-    </row>
-    <row r="104" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B104" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C104" s="22"/>
-      <c r="D104" s="22"/>
-      <c r="E104" s="22"/>
-      <c r="F104" s="22"/>
-      <c r="G104" s="22"/>
-      <c r="H104" s="22"/>
-    </row>
-    <row r="105" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B105" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C105" s="22"/>
-      <c r="D105" s="22"/>
-      <c r="E105" s="22"/>
-      <c r="F105" s="22"/>
-      <c r="G105" s="22"/>
-      <c r="H105" s="22"/>
-    </row>
-    <row r="106" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B106" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C106" s="22"/>
-      <c r="D106" s="22"/>
-      <c r="E106" s="22"/>
-      <c r="F106" s="22"/>
-      <c r="G106" s="22"/>
-      <c r="H106" s="22"/>
-    </row>
-    <row r="109" ht="15">
-      <c r="B109" s="22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="124" ht="15">
-      <c r="B124" s="22" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="125" ht="15">
-      <c r="B125" s="22" t="s">
-        <v>145</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B106:H106"/>
-    <mergeCell ref="B101:H101"/>
-    <mergeCell ref="B102:H102"/>
-    <mergeCell ref="B103:H103"/>
-    <mergeCell ref="B104:H104"/>
-    <mergeCell ref="B105:H105"/>
+  <mergeCells count="10">
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B97:H97"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B96:I96"/>
-    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="B88:I88"/>
+    <mergeCell ref="B92:I92"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
